--- a/Archived_HE_Data/hedata_2026-09-07.xlsx
+++ b/Archived_HE_Data/hedata_2026-09-07.xlsx
@@ -2227,10 +2227,10 @@
     <t>Adjunct Nursing Clinical Instructor (CRRN)</t>
   </si>
   <si>
+    <t>https://www.schooljobs.com/careers/ummissoula/jobs/4694471/adjunct-nursing-clinical-instructor-crrn</t>
+  </si>
+  <si>
     <t>https://www.schooljobs.com/careers/ummissoula/jobs/4993102/adjunct-nursing-clinical-instructor-crrn</t>
-  </si>
-  <si>
-    <t>https://www.schooljobs.com/careers/ummissoula/jobs/4694471/adjunct-nursing-clinical-instructor-crrn</t>
   </si>
   <si>
     <t>Administrartive Associate III</t>
